--- a/CAPSTONE/bus311-capstone-red-team-record.xlsx
+++ b/CAPSTONE/bus311-capstone-red-team-record.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Record" sheetId="1" r:id="R67c400c7a8ca4db8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checkpoint Log" sheetId="2" r:id="R51eca95ddc4b42fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Record" sheetId="1" r:id="R9bbca9110c824370"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checkpoint Log" sheetId="2" r:id="R019c04365daa45a9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -610,7 +610,7 @@
         <x:color rgb="FF175C2C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE7F4EA"/>
         </x:patternFill>
       </x:fill>
@@ -621,7 +621,7 @@
         <x:color rgb="FF8A1C1C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -1193,7 +1193,7 @@
     </x:row>
     <x:row r="33" ht="24" customHeight="1">
       <x:c r="A33" s="42" t="str">
-        <x:v>7 | BOARD Q&amp;A REVISION</x:v>
+        <x:v>7 | ORAL BOARD PRESENTATION REVISION</x:v>
       </x:c>
       <x:c r="B33" s="43"/>
       <x:c r="C33" s="43"/>
@@ -1205,7 +1205,7 @@
     </x:row>
     <x:row r="34" ht="24" customHeight="1">
       <x:c r="A34" s="93" t="str">
-        <x:v>INSTRUCTION - REPLACE: Identify the weakest revenue, valuation, implementation, or risk answer; the evidence rechecked; and the revision made to your deck, executive summary, recommendation, model support, or speaking notes.</x:v>
+        <x:v>INSTRUCTION - REPLACE: Identify the weakest revenue, valuation, implementation, or risk response; the evidence rechecked; and the revision made to your PowerPoint company analysis, recommendation, model support, or speaking notes.</x:v>
       </x:c>
       <x:c r="B34" s="74"/>
       <x:c r="C34" s="74"/>
@@ -1466,7 +1466,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="115" t="str">
-        <x:v>Board Q&amp;A: revenue, valuation, implementation, risk</x:v>
+        <x:v>Oral Board presentation: decision briefing plus live questions about revenue, valuation, implementation, and risk</x:v>
       </x:c>
       <x:c r="C8" s="18"/>
       <x:c r="D8" s="18"/>

--- a/CAPSTONE/bus311-capstone-red-team-record.xlsx
+++ b/CAPSTONE/bus311-capstone-red-team-record.xlsx
@@ -90,7 +90,7 @@
     <t>6 | REVISED REVENUE HYPOTHESIS</t>
   </si>
   <si>
-    <t>7 | ORAL BOARD PRESENTATION REVISION</t>
+    <t>7 | ORAL PRESENTATION REVISION</t>
   </si>
   <si>
     <t>INSTRUCTION - REPLACE: Identify the weakest revenue, valuation, implementation, or risk response; the evidence rechecked; and the revision made to your PowerPoint company analysis, recommendation, model support, or speaking notes.</t>
@@ -153,7 +153,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>Oral Board presentation: decision briefing plus live questions about revenue, valuation, implementation, and risk</t>
+    <t>Oral Presentation: decision briefing plus live questions about revenue, valuation, implementation, and risk</t>
   </si>
 </sst>
 </file>
